--- a/协作/模板/36-追溯矩阵.xlsx
+++ b/协作/模板/36-追溯矩阵.xlsx
@@ -2229,8 +2229,8 @@
     <dataValidation sqref="J2:J121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
       <formula1>"passed,blocked"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
-      <formula1>"完整,断链"</formula1>
+    <dataValidation sqref="L2:L121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"完整,断链,已验收"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
